--- a/InputData/trans/FoSfBPPTtC/Fraction of Subsidy for Battery Production Passed Through to Consumers.xlsx
+++ b/InputData/trans/FoSfBPPTtC/Fraction of Subsidy for Battery Production Passed Through to Consumers.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modeling\EPS\US\eps-us\InputData\trans\FoSfBPPTtC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\trans\FoSfBPPTtC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF4B6996-70C7-475C-BE74-6F9B5267381C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E1232FB-AC72-4B08-A84C-F862671FD419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="59580" yWindow="1425" windowWidth="21600" windowHeight="15210" activeTab="1" xr2:uid="{DC12087C-9A27-4A43-B4A9-6B3F1E517F08}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{DC12087C-9A27-4A43-B4A9-6B3F1E517F08}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -582,10 +582,10 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="D2">
         <v>0.25</v>
@@ -618,58 +618,58 @@
         <v>0.5</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
